--- a/Conditional Formatting.xlsx
+++ b/Conditional Formatting.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E412F67-DCE0-4FFD-8E98-B9A7D827A2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48B8C0D-385A-4C4C-AA7E-116A0649E85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{738BFFA1-D504-4F3D-A6A7-73B996B5C8AB}"/>
   </bookViews>
@@ -271,67 +271,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -364,36 +313,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -414,21 +333,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -484,11 +393,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -504,141 +433,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -966,1079 +765,1066 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="L2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="M2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="O2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="P2" s="3">
+      <c r="G2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="M2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="N2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="P2" s="2">
         <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>12000</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>12000</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>12000</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>12000</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <v>12000</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>12000</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>12000</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>12000</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <v>12000</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="H4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="I4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="J4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="K4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="L4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="M4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="N4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="O4" s="3">
-        <v>11250</v>
-      </c>
-      <c r="P4" s="3">
+      <c r="G4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="H4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="I4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="J4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="K4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="L4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="M4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="N4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="O4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="P4" s="2">
         <v>11250</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>12000</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>12000</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>12000</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>12000</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>12000</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>12000</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>12000</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>12000</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>12000</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>12000</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>16250</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>16250</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>16250</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>16250</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>16250</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>16250</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>16250</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <v>16250</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <v>16250</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>16250</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>6400</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>6400</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>6400</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>6400</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>6400</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>6400</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>6400</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <v>6400</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="2">
         <v>6400</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>6400</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>4500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>4500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>4500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>4500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="2">
         <v>4500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="2">
         <v>4500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="2">
         <v>4500</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>6275</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>6275</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>6275</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>6275</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>6275</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>6275</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>6275</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <v>6275</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="2">
         <v>6275</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>6275</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>6250</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>6250</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <v>6250</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>6250</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <v>6250</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>6250</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <v>6250</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <v>6250</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="2">
         <v>6250</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>6250</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>8750</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>8750</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>8750</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>8750</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>8750</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>8750</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <v>8750</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>8750</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="2">
         <v>8750</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>8750</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="H12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="I12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="J12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="K12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="L12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="M12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="N12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="O12" s="3">
-        <v>11250</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="G12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="H12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="I12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="J12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="K12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="L12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="M12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="N12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="O12" s="2">
+        <v>11250</v>
+      </c>
+      <c r="P12" s="2">
         <v>11250</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="L13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="M13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="O13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="P13" s="3">
+      <c r="G13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="M13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="N13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="P13" s="2">
         <v>10000</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>16250</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>16250</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <v>16250</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <v>16250</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="2">
         <v>16250</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="2">
         <v>16250</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="2">
         <v>16250</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="2">
         <v>16250</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="2">
         <v>16250</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="2">
         <v>16250</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>6400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>6400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <v>6400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <v>6400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="2">
         <v>6400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="2">
         <v>6400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="2">
         <v>6400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="2">
         <v>6400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="2">
         <v>6400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="2">
         <v>6400</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>4500</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>4500</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <v>4500</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <v>4500</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="2">
         <v>4500</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="2">
         <v>4500</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="2">
         <v>4500</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="2">
         <v>4500</v>
       </c>
-      <c r="O16" s="3">
+      <c r="O16" s="2">
         <v>4500</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="2">
         <v>4500</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>6275</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <v>6275</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <v>6275</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <v>6275</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="2">
         <v>6275</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <v>6275</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="2">
         <v>6275</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="2">
         <v>6275</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="2">
         <v>6275</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="2">
         <v>6275</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>6250</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>6250</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <v>6250</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <v>6250</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="2">
         <v>6250</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="2">
         <v>6250</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="2">
         <v>6250</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="2">
         <v>6250</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="2">
         <v>6250</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="2">
         <v>6250</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>8750</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <v>8750</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <v>8750</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>8750</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="2">
         <v>8750</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="2">
         <v>8750</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="2">
         <v>8750</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="2">
         <v>8750</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O19" s="2">
         <v>8750</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="2">
         <v>8750</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="H20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="I20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="J20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="K20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="L20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="M20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="N20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="O20" s="3">
-        <v>11250</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="G20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="H20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="I20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="J20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="K20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="L20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="M20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="N20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="O20" s="2">
+        <v>11250</v>
+      </c>
+      <c r="P20" s="2">
         <v>11250</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>10000</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="G21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="M21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="N21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="P21" s="2">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N21">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
+  <conditionalFormatting sqref="G2:G21">
+    <cfRule type="top10" dxfId="15" priority="4" rank="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
-    <cfRule type="iconSet" priority="10">
-      <iconSet iconSet="3Signs">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
-    </cfRule>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="top10" dxfId="14" priority="5" percent="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I21">
+    <cfRule type="top10" dxfId="13" priority="3" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="12" priority="6" bottom="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J21">
+    <cfRule type="top10" dxfId="11" priority="2" percent="1" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="10" priority="7" percent="1" bottom="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K21">
+    <cfRule type="aboveAverage" dxfId="9" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L21">
+    <cfRule type="aboveAverage" dxfId="8" priority="9" aboveAverage="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M21">
-    <cfRule type="dataBar" priority="9">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2051,27 +1837,50 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
-    <cfRule type="aboveAverage" dxfId="14" priority="8" aboveAverage="0"/>
+  <conditionalFormatting sqref="N2:N21">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
-    <cfRule type="aboveAverage" dxfId="13" priority="7"/>
+  <conditionalFormatting sqref="O2:O21">
+    <cfRule type="iconSet" priority="11">
+      <iconSet iconSet="3Signs">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
-    <cfRule type="top10" dxfId="0" priority="6" percent="1" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="1" priority="1" percent="1" bottom="1" rank="10"/>
+  <conditionalFormatting sqref="P2:P21">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9E988C47-DBD1-4E7C-B892-CC3B579C6DB4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
-    <cfRule type="top10" dxfId="12" priority="5" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="11" priority="2" bottom="1" rank="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
-    <cfRule type="top10" dxfId="10" priority="4" percent="1" rank="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
-    <cfRule type="top10" dxfId="9" priority="3" rank="10"/>
-  </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B21" xr:uid="{19A77D5B-23FA-436A-9073-51E5CB97AEFA}">
       <formula1>ISTEXT(B1)</formula1>
     </dataValidation>
@@ -2099,6 +1908,17 @@
           </x14:cfRule>
           <xm:sqref>M2:M21</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9E988C47-DBD1-4E7C-B892-CC3B579C6DB4}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P2:P21</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
